--- a/data/mock_students.xlsx
+++ b/data/mock_students.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,11 @@
           <t>Period</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -478,6 +483,11 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,6 +511,11 @@
       <c r="E3" t="n">
         <v>1</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -524,6 +539,11 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -547,6 +567,11 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -570,6 +595,11 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -593,6 +623,11 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -616,6 +651,11 @@
       <c r="E8" t="n">
         <v>1</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -639,6 +679,11 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -662,6 +707,11 @@
       <c r="E10" t="n">
         <v>1</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -685,6 +735,11 @@
       <c r="E11" t="n">
         <v>2</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -708,6 +763,11 @@
       <c r="E12" t="n">
         <v>2</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -731,6 +791,11 @@
       <c r="E13" t="n">
         <v>2</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -754,6 +819,11 @@
       <c r="E14" t="n">
         <v>2</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -777,6 +847,11 @@
       <c r="E15" t="n">
         <v>2</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -800,6 +875,11 @@
       <c r="E16" t="n">
         <v>2</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -823,6 +903,11 @@
       <c r="E17" t="n">
         <v>2</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -846,6 +931,11 @@
       <c r="E18" t="n">
         <v>2</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -869,6 +959,11 @@
       <c r="E19" t="n">
         <v>2</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -892,6 +987,11 @@
       <c r="E20" t="n">
         <v>3</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -915,6 +1015,11 @@
       <c r="E21" t="n">
         <v>3</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -938,6 +1043,11 @@
       <c r="E22" t="n">
         <v>3</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -961,6 +1071,11 @@
       <c r="E23" t="n">
         <v>3</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -984,6 +1099,11 @@
       <c r="E24" t="n">
         <v>3</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1007,6 +1127,11 @@
       <c r="E25" t="n">
         <v>3</v>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1030,6 +1155,11 @@
       <c r="E26" t="n">
         <v>3</v>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1053,6 +1183,11 @@
       <c r="E27" t="n">
         <v>3</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1076,6 +1211,11 @@
       <c r="E28" t="n">
         <v>3</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1099,6 +1239,11 @@
       <c r="E29" t="n">
         <v>4</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1122,6 +1267,11 @@
       <c r="E30" t="n">
         <v>4</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1145,6 +1295,11 @@
       <c r="E31" t="n">
         <v>4</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1168,6 +1323,11 @@
       <c r="E32" t="n">
         <v>4</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1191,6 +1351,11 @@
       <c r="E33" t="n">
         <v>4</v>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1214,6 +1379,11 @@
       <c r="E34" t="n">
         <v>4</v>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1237,6 +1407,11 @@
       <c r="E35" t="n">
         <v>4</v>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1260,6 +1435,11 @@
       <c r="E36" t="n">
         <v>4</v>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1283,6 +1463,11 @@
       <c r="E37" t="n">
         <v>4</v>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1306,6 +1491,11 @@
       <c r="E38" t="n">
         <v>5</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1329,6 +1519,11 @@
       <c r="E39" t="n">
         <v>5</v>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1352,6 +1547,11 @@
       <c r="E40" t="n">
         <v>5</v>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1375,6 +1575,11 @@
       <c r="E41" t="n">
         <v>5</v>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1398,6 +1603,11 @@
       <c r="E42" t="n">
         <v>5</v>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1421,6 +1631,11 @@
       <c r="E43" t="n">
         <v>5</v>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1444,6 +1659,11 @@
       <c r="E44" t="n">
         <v>5</v>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1467,6 +1687,11 @@
       <c r="E45" t="n">
         <v>5</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1490,6 +1715,11 @@
       <c r="E46" t="n">
         <v>5</v>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1513,6 +1743,11 @@
       <c r="E47" t="n">
         <v>6</v>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1536,6 +1771,11 @@
       <c r="E48" t="n">
         <v>6</v>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1559,6 +1799,11 @@
       <c r="E49" t="n">
         <v>6</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1582,6 +1827,11 @@
       <c r="E50" t="n">
         <v>6</v>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1605,6 +1855,11 @@
       <c r="E51" t="n">
         <v>6</v>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1628,6 +1883,11 @@
       <c r="E52" t="n">
         <v>6</v>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1651,6 +1911,11 @@
       <c r="E53" t="n">
         <v>6</v>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1674,6 +1939,11 @@
       <c r="E54" t="n">
         <v>6</v>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1697,6 +1967,11 @@
       <c r="E55" t="n">
         <v>6</v>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1720,6 +1995,11 @@
       <c r="E56" t="n">
         <v>1</v>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1743,6 +2023,11 @@
       <c r="E57" t="n">
         <v>1</v>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1766,6 +2051,11 @@
       <c r="E58" t="n">
         <v>1</v>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1789,6 +2079,11 @@
       <c r="E59" t="n">
         <v>1</v>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1812,6 +2107,11 @@
       <c r="E60" t="n">
         <v>1</v>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1835,6 +2135,11 @@
       <c r="E61" t="n">
         <v>1</v>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1858,6 +2163,11 @@
       <c r="E62" t="n">
         <v>1</v>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1881,6 +2191,11 @@
       <c r="E63" t="n">
         <v>1</v>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1904,6 +2219,11 @@
       <c r="E64" t="n">
         <v>1</v>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1927,6 +2247,11 @@
       <c r="E65" t="n">
         <v>2</v>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1950,6 +2275,11 @@
       <c r="E66" t="n">
         <v>2</v>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1973,6 +2303,11 @@
       <c r="E67" t="n">
         <v>2</v>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1996,6 +2331,11 @@
       <c r="E68" t="n">
         <v>2</v>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2019,6 +2359,11 @@
       <c r="E69" t="n">
         <v>2</v>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2042,6 +2387,11 @@
       <c r="E70" t="n">
         <v>2</v>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2065,6 +2415,11 @@
       <c r="E71" t="n">
         <v>2</v>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2088,6 +2443,11 @@
       <c r="E72" t="n">
         <v>2</v>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2111,6 +2471,11 @@
       <c r="E73" t="n">
         <v>2</v>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2134,6 +2499,11 @@
       <c r="E74" t="n">
         <v>3</v>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2157,6 +2527,11 @@
       <c r="E75" t="n">
         <v>3</v>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2180,6 +2555,11 @@
       <c r="E76" t="n">
         <v>3</v>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2203,6 +2583,11 @@
       <c r="E77" t="n">
         <v>3</v>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2226,6 +2611,11 @@
       <c r="E78" t="n">
         <v>3</v>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2249,6 +2639,11 @@
       <c r="E79" t="n">
         <v>3</v>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2272,6 +2667,11 @@
       <c r="E80" t="n">
         <v>3</v>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2295,6 +2695,11 @@
       <c r="E81" t="n">
         <v>3</v>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2318,6 +2723,11 @@
       <c r="E82" t="n">
         <v>3</v>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2341,6 +2751,11 @@
       <c r="E83" t="n">
         <v>4</v>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2364,6 +2779,11 @@
       <c r="E84" t="n">
         <v>4</v>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2387,6 +2807,11 @@
       <c r="E85" t="n">
         <v>4</v>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2410,6 +2835,11 @@
       <c r="E86" t="n">
         <v>4</v>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2433,6 +2863,11 @@
       <c r="E87" t="n">
         <v>4</v>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2456,6 +2891,11 @@
       <c r="E88" t="n">
         <v>4</v>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2479,6 +2919,11 @@
       <c r="E89" t="n">
         <v>4</v>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2502,6 +2947,11 @@
       <c r="E90" t="n">
         <v>4</v>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2525,6 +2975,11 @@
       <c r="E91" t="n">
         <v>4</v>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2548,6 +3003,11 @@
       <c r="E92" t="n">
         <v>5</v>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2571,6 +3031,11 @@
       <c r="E93" t="n">
         <v>5</v>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2594,6 +3059,11 @@
       <c r="E94" t="n">
         <v>5</v>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2617,6 +3087,11 @@
       <c r="E95" t="n">
         <v>5</v>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2640,6 +3115,11 @@
       <c r="E96" t="n">
         <v>5</v>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2663,6 +3143,11 @@
       <c r="E97" t="n">
         <v>5</v>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2686,6 +3171,11 @@
       <c r="E98" t="n">
         <v>5</v>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2709,6 +3199,11 @@
       <c r="E99" t="n">
         <v>5</v>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2732,6 +3227,11 @@
       <c r="E100" t="n">
         <v>5</v>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2755,6 +3255,11 @@
       <c r="E101" t="n">
         <v>6</v>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2778,6 +3283,11 @@
       <c r="E102" t="n">
         <v>6</v>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2801,6 +3311,11 @@
       <c r="E103" t="n">
         <v>6</v>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2824,6 +3339,11 @@
       <c r="E104" t="n">
         <v>6</v>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2847,6 +3367,11 @@
       <c r="E105" t="n">
         <v>6</v>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2870,6 +3395,11 @@
       <c r="E106" t="n">
         <v>6</v>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2893,6 +3423,11 @@
       <c r="E107" t="n">
         <v>6</v>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2916,6 +3451,11 @@
       <c r="E108" t="n">
         <v>6</v>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2939,6 +3479,11 @@
       <c r="E109" t="n">
         <v>6</v>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2962,6 +3507,11 @@
       <c r="E110" t="n">
         <v>1</v>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2985,6 +3535,11 @@
       <c r="E111" t="n">
         <v>1</v>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3008,6 +3563,11 @@
       <c r="E112" t="n">
         <v>1</v>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3031,6 +3591,11 @@
       <c r="E113" t="n">
         <v>1</v>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3054,6 +3619,11 @@
       <c r="E114" t="n">
         <v>1</v>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3077,6 +3647,11 @@
       <c r="E115" t="n">
         <v>1</v>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3100,6 +3675,11 @@
       <c r="E116" t="n">
         <v>1</v>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3123,6 +3703,11 @@
       <c r="E117" t="n">
         <v>1</v>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3146,6 +3731,11 @@
       <c r="E118" t="n">
         <v>1</v>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3169,6 +3759,11 @@
       <c r="E119" t="n">
         <v>2</v>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3192,6 +3787,11 @@
       <c r="E120" t="n">
         <v>2</v>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3215,6 +3815,11 @@
       <c r="E121" t="n">
         <v>2</v>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3238,6 +3843,11 @@
       <c r="E122" t="n">
         <v>2</v>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3261,6 +3871,11 @@
       <c r="E123" t="n">
         <v>2</v>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3284,6 +3899,11 @@
       <c r="E124" t="n">
         <v>2</v>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3307,6 +3927,11 @@
       <c r="E125" t="n">
         <v>2</v>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3330,6 +3955,11 @@
       <c r="E126" t="n">
         <v>2</v>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3353,6 +3983,11 @@
       <c r="E127" t="n">
         <v>2</v>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3376,6 +4011,11 @@
       <c r="E128" t="n">
         <v>3</v>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3399,6 +4039,11 @@
       <c r="E129" t="n">
         <v>3</v>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3422,6 +4067,11 @@
       <c r="E130" t="n">
         <v>3</v>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3445,6 +4095,11 @@
       <c r="E131" t="n">
         <v>3</v>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3468,6 +4123,11 @@
       <c r="E132" t="n">
         <v>3</v>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3491,6 +4151,11 @@
       <c r="E133" t="n">
         <v>3</v>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3514,6 +4179,11 @@
       <c r="E134" t="n">
         <v>3</v>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3537,6 +4207,11 @@
       <c r="E135" t="n">
         <v>3</v>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3560,6 +4235,11 @@
       <c r="E136" t="n">
         <v>3</v>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3583,6 +4263,11 @@
       <c r="E137" t="n">
         <v>4</v>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3606,6 +4291,11 @@
       <c r="E138" t="n">
         <v>4</v>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3629,6 +4319,11 @@
       <c r="E139" t="n">
         <v>4</v>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3652,6 +4347,11 @@
       <c r="E140" t="n">
         <v>4</v>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3675,6 +4375,11 @@
       <c r="E141" t="n">
         <v>4</v>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3698,6 +4403,11 @@
       <c r="E142" t="n">
         <v>4</v>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3721,6 +4431,11 @@
       <c r="E143" t="n">
         <v>4</v>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3744,6 +4459,11 @@
       <c r="E144" t="n">
         <v>4</v>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3767,6 +4487,11 @@
       <c r="E145" t="n">
         <v>4</v>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3790,6 +4515,11 @@
       <c r="E146" t="n">
         <v>5</v>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3813,6 +4543,11 @@
       <c r="E147" t="n">
         <v>5</v>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3836,6 +4571,11 @@
       <c r="E148" t="n">
         <v>5</v>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3859,6 +4599,11 @@
       <c r="E149" t="n">
         <v>5</v>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3882,6 +4627,11 @@
       <c r="E150" t="n">
         <v>5</v>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3905,6 +4655,11 @@
       <c r="E151" t="n">
         <v>5</v>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3928,6 +4683,11 @@
       <c r="E152" t="n">
         <v>5</v>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3951,6 +4711,11 @@
       <c r="E153" t="n">
         <v>5</v>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3974,6 +4739,11 @@
       <c r="E154" t="n">
         <v>5</v>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3997,6 +4767,11 @@
       <c r="E155" t="n">
         <v>6</v>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4020,6 +4795,11 @@
       <c r="E156" t="n">
         <v>6</v>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4043,6 +4823,11 @@
       <c r="E157" t="n">
         <v>6</v>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4066,6 +4851,11 @@
       <c r="E158" t="n">
         <v>6</v>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4089,6 +4879,11 @@
       <c r="E159" t="n">
         <v>6</v>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4112,6 +4907,11 @@
       <c r="E160" t="n">
         <v>6</v>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4135,6 +4935,11 @@
       <c r="E161" t="n">
         <v>6</v>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4158,6 +4963,11 @@
       <c r="E162" t="n">
         <v>6</v>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4180,6 +4990,11 @@
       </c>
       <c r="E163" t="n">
         <v>6</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
       </c>
     </row>
   </sheetData>
